--- a/stories/arbres/TREE-SAN-014.xlsx
+++ b/stories/arbres/TREE-SAN-014.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a passé l'après-midi au marché avec papa. Maman les attend. Les sacs sont posés. Il fait nuit. Le soir, on met le pyjama. Puis c'est le dodo. Le corps a besoin de dormir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1511,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Le sac rouge est près de la porte. Le soir, Sami met son pyjama. Papa l'aide. Maman ouvre le lit. Sami se couche. C'est le dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rentre du marché. Que met-il ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Le sac rouge attend. Sami a le pyjama. Le soir, dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2189,6 +2231,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -2353,6 +2400,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon rouge reste au salon. Sami a le pyjama. Le soir, il se couche. Dodo. Papa baisse la lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2539,6 +2591,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2701,6 +2758,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat peluche est sur l'oreiller. Sami a le pyjama. Le soir, dodo. Papa baisse la lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2925,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3092,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien peluche est au pied. Sami a mis le pyjama. Le soir, dodo. Maman chuchote.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3259,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3426,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|La poule peluche est ronde. Sami se couche. Le soir, dodo. Le sac rouge attend.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Le seau bleu reste à la cuisine. Le soir, Sami a le pyjama. Au lit. Dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3859,6 +3951,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4021,6 +4118,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat peluche ronronne. Sami a le pyjama. Le soir, dodo. Le seau bleu reste à la cuisine.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4285,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4452,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien peluche garde. Sami a mis le pyjama. Le soir, dodo. Une pomme sent encore.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4619,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4786,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|La poule peluche est sous le bras. Sami, dodo. Le soir. Il respire.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4953,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5120,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou va au lit. Sami aussi. Le soir, pyjama. Dodo. Maman chuchote.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5179,6 +5311,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5341,6 +5478,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat peluche et le doudou. Sami a le pyjama. Le soir, dodo. Maman pose un baiser.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5645,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5812,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien peluche près du doudou. Sami a mis le pyjama. Le soir, dodo. Le salon s'éteint.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5979,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6146,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|La poule peluche et le doudou. Sami se couche. Le soir, dodo. Silence.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6313,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6342,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Le sac bleu sent le pain. Le soir, Sami met son pyjama. Il est doux. Il se couche. C'est le dodo. Papa dit : le corps a besoin de dormir.</t>
+          <t>Le sac bleu sent le pain. Le soir, Sami met son pyjama. Il est doux. Il se couche. C'est le dodo. Le corps a besoin de dormir.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6480,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Le sac bleu sent le pain. Le soir, Sami met son pyjama. Il est doux. Il se couche. C'est le dodo.
+papa|Le corps a besoin de dormir.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6662,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Le sac bleu est posé. Sami met quoi ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6835,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain attendra demain. Sami a le pyjama. Le soir, dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6849,6 +7032,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -7013,6 +7201,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon rouge reste. Sami a le pyjama. Le soir, au lit. Dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7199,6 +7392,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7361,6 +7559,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat peluche veille. Sami a le pyjama. Le soir, dodo. Le sac bleu sent le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7726,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7893,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien peluche veille. Sami a mis le pyjama. Le soir, dodo. Papa raconte deux phrases.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8060,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8227,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|La poule peluche veille. Sami se couche. Le soir, dodo. Le pain attendra demain.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8394,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8561,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Le seau bleu est rangé. Le soir, pyjama. Sami se couche. Dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8519,6 +8752,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8681,6 +8919,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat peluche ferme un œil. Sami a le pyjama. Le soir, dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9086,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9253,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien peluche a une oreille sur l'oreiller. Sami a mis le pyjama. Le soir, dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9420,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9587,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|La poule peluche est ronde et chaude. Sami, dodo. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9754,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9921,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou sent le savon. Sami a le pyjama. Le soir, dodo. Maman pose un baiser.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9839,6 +10112,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10001,6 +10279,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat peluche et le doudou sentent le savon. Sami a le pyjama. Le soir, dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10163,6 +10446,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10325,6 +10613,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien peluche et le doudou. Sami a mis le pyjama. Le soir, dodo. Maman baisse le store.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10487,6 +10780,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10511,7 +10809,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>La poule peluche et le doudou. Sami se couche. Le soir, dodo. Papa dit : demain.</t>
+          <t>La poule peluche et le doudou. Sami se couche. Le soir, dodo. Demain.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10649,6 +10947,12 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|La poule peluche et le doudou. Sami se couche. Le soir, dodo.
+papa|Demain.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10811,6 +11115,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10973,6 +11282,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Le sac vert a des pommes. Le soir, Sami met son pyjama. Maman boutonne. Il se couche. C'est le dodo. Papa raconte deux phrases.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11149,6 +11463,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Le sac vert est posé. Sami met quoi pour dormir ?</t>
         </is>
       </c>
     </row>
@@ -11317,6 +11636,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Les pommes dormiront dans le plat. Sami a le pyjama. Le soir, dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11509,6 +11833,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -11673,6 +12002,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon rouge reste au couloir. Sami a le pyjama. Le soir, dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11859,6 +12193,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12021,6 +12360,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat peluche. Sami a le pyjama. Le soir, dodo. Le sac vert a des pommes.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12527,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12694,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien peluche. Sami a mis le pyjama. Le soir, dodo. Les pommes dormiront dans le plat.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12861,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13028,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|La poule peluche. Sami se couche. Le soir, dodo. Le ballon reste au couloir.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13195,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13362,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Le seau bleu reste près des pommes. Le soir, pyjama. Sami au lit. Dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13179,6 +13553,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13341,6 +13720,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat peluche. Sami a le pyjama. Le soir, dodo. Le seau bleu reste près des pommes.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13503,6 +13887,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13665,6 +14054,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien peluche. Sami a mis le pyjama. Le soir, dodo. Une pomme roule, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13827,6 +14221,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13989,6 +14388,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|La poule peluche. Sami, dodo. Le soir. Il ferme les yeux.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14151,6 +14555,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14313,6 +14722,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou retrouve l'oreiller. Sami a le pyjama. Le soir, dodo. La maison est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14499,6 +14913,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14661,6 +15080,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat peluche et le doudou. Sami a le pyjama. Le soir, dodo. La maison est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14823,6 +15247,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14985,6 +15414,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien peluche et le doudou. Sami a mis le pyjama. Le soir, dodo. On entend la rue, loin.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15147,6 +15581,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15309,6 +15748,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|La poule peluche et le doudou. Sami se couche. Le soir, dodo. Maman ferme la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15471,6 +15915,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15489,7 +15938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15527,6 +15976,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-014.xlsx
+++ b/stories/arbres/TREE-SAN-014.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Sami a passé l'après-midi au marché avec papa. Maman les attend. Les sacs sont posés. Il fait nuit. Le soir, on met le pyjama. Puis c'est le dodo. Le corps a besoin de dormir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Le sac rouge est près de la porte. Le soir, Sami met son pyjama. Papa l'aide. Maman ouvre le lit. Sami se couche. C'est le dodo.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|Sami rentre du marché. Que met-il ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Le sac rouge attend. Sami a le pyjama. Le soir, dodo.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2238,6 +2248,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2405,6 +2416,7 @@
           <t>narrateur|Le ballon rouge reste au salon. Sami a le pyjama. Le soir, il se couche. Dodo. Papa baisse la lumière.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2594,6 +2606,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2763,6 +2780,7 @@
           <t>narrateur|Le chat peluche est sur l'oreiller. Sami a le pyjama. Le soir, dodo. Papa baisse la lumière.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2930,6 +2948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3097,6 +3116,11 @@
           <t>narrateur|Le chien peluche est au pied. Sami a mis le pyjama. Le soir, dodo. Maman chuchote.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3264,6 +3288,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3456,7 @@
           <t>narrateur|La poule peluche est ronde. Sami se couche. Le soir, dodo. Le sac rouge attend.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3624,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3792,7 @@
           <t>narrateur|Le seau bleu reste à la cuisine. Le soir, Sami a le pyjama. Au lit. Dodo.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3954,6 +3982,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4123,6 +4156,7 @@
           <t>narrateur|Le chat peluche ronronne. Sami a le pyjama. Le soir, dodo. Le seau bleu reste à la cuisine.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4290,6 +4324,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4457,6 +4492,11 @@
           <t>narrateur|Le chien peluche garde. Sami a mis le pyjama. Le soir, dodo. Une pomme sent encore.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4624,6 +4664,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4791,6 +4832,7 @@
           <t>narrateur|La poule peluche est sous le bras. Sami, dodo. Le soir. Il respire.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4958,6 +5000,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5125,6 +5168,7 @@
           <t>narrateur|Le doudou va au lit. Sami aussi. Le soir, pyjama. Dodo. Maman chuchote.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5314,6 +5358,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5483,6 +5532,7 @@
           <t>narrateur|Le chat peluche et le doudou. Sami a le pyjama. Le soir, dodo. Maman pose un baiser.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5650,6 +5700,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5817,6 +5868,11 @@
           <t>narrateur|Le chien peluche près du doudou. Sami a mis le pyjama. Le soir, dodo. Le salon s'éteint.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5984,6 +6040,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6151,6 +6208,7 @@
           <t>narrateur|La poule peluche et le doudou. Sami se couche. Le soir, dodo. Silence.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6318,6 +6376,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6486,6 +6545,7 @@
 papa|Le corps a besoin de dormir.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6669,6 +6729,7 @@
           <t>narrateur|Le sac bleu est posé. Sami met quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6840,6 +6901,7 @@
           <t>narrateur|Le pain attendra demain. Sami a le pyjama. Le soir, dodo.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7039,6 +7101,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7206,6 +7269,7 @@
           <t>narrateur|Le ballon rouge reste. Sami a le pyjama. Le soir, au lit. Dodo.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7395,6 +7459,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7564,6 +7633,7 @@
           <t>narrateur|Le chat peluche veille. Sami a le pyjama. Le soir, dodo. Le sac bleu sent le pain.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7731,6 +7801,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7898,6 +7969,11 @@
           <t>narrateur|Le chien peluche veille. Sami a mis le pyjama. Le soir, dodo. Papa raconte deux phrases.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8065,6 +8141,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8232,6 +8309,7 @@
           <t>narrateur|La poule peluche veille. Sami se couche. Le soir, dodo. Le pain attendra demain.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8399,6 +8477,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8566,6 +8645,7 @@
           <t>narrateur|Le seau bleu est rangé. Le soir, pyjama. Sami se couche. Dodo.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8755,6 +8835,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8924,6 +9009,7 @@
           <t>narrateur|Le chat peluche ferme un œil. Sami a le pyjama. Le soir, dodo.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9091,6 +9177,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9258,6 +9345,11 @@
           <t>narrateur|Le chien peluche a une oreille sur l'oreiller. Sami a mis le pyjama. Le soir, dodo.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9425,6 +9517,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9592,6 +9685,7 @@
           <t>narrateur|La poule peluche est ronde et chaude. Sami, dodo. Le soir.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9759,6 +9853,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9926,6 +10021,7 @@
           <t>narrateur|Le doudou sent le savon. Sami a le pyjama. Le soir, dodo. Maman pose un baiser.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10115,6 +10211,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10284,6 +10385,7 @@
           <t>narrateur|Le chat peluche et le doudou sentent le savon. Sami a le pyjama. Le soir, dodo.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10451,6 +10553,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10618,6 +10721,11 @@
           <t>narrateur|Le chien peluche et le doudou. Sami a mis le pyjama. Le soir, dodo. Maman baisse le store.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10785,6 +10893,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10953,6 +11062,7 @@
 papa|Demain.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11120,6 +11230,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11287,6 +11398,7 @@
           <t>narrateur|Le sac vert a des pommes. Le soir, Sami met son pyjama. Maman boutonne. Il se couche. C'est le dodo. Papa raconte deux phrases.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11470,6 +11582,7 @@
           <t>narrateur|Le sac vert est posé. Sami met quoi pour dormir ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11641,6 +11754,7 @@
           <t>narrateur|Les pommes dormiront dans le plat. Sami a le pyjama. Le soir, dodo.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11840,6 +11954,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12007,6 +12122,7 @@
           <t>narrateur|Le ballon rouge reste au couloir. Sami a le pyjama. Le soir, dodo.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12196,6 +12312,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12365,6 +12486,7 @@
           <t>narrateur|Le chat peluche. Sami a le pyjama. Le soir, dodo. Le sac vert a des pommes.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12532,6 +12654,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12699,6 +12822,11 @@
           <t>narrateur|Le chien peluche. Sami a mis le pyjama. Le soir, dodo. Les pommes dormiront dans le plat.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12866,6 +12994,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13033,6 +13162,7 @@
           <t>narrateur|La poule peluche. Sami se couche. Le soir, dodo. Le ballon reste au couloir.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13200,6 +13330,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13367,6 +13498,7 @@
           <t>narrateur|Le seau bleu reste près des pommes. Le soir, pyjama. Sami au lit. Dodo.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13556,6 +13688,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13725,6 +13862,7 @@
           <t>narrateur|Le chat peluche. Sami a le pyjama. Le soir, dodo. Le seau bleu reste près des pommes.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13892,6 +14030,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14059,6 +14198,11 @@
           <t>narrateur|Le chien peluche. Sami a mis le pyjama. Le soir, dodo. Une pomme roule, tout doux.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14226,6 +14370,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14393,6 +14538,7 @@
           <t>narrateur|La poule peluche. Sami, dodo. Le soir. Il ferme les yeux.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14560,6 +14706,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14727,6 +14874,7 @@
           <t>narrateur|Le doudou retrouve l'oreiller. Sami a le pyjama. Le soir, dodo. La maison est calme.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14916,6 +15064,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15085,6 +15238,7 @@
           <t>narrateur|Le chat peluche et le doudou. Sami a le pyjama. Le soir, dodo. La maison est calme.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15252,6 +15406,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15419,6 +15574,11 @@
           <t>narrateur|Le chien peluche et le doudou. Sami a mis le pyjama. Le soir, dodo. On entend la rue, loin.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15586,6 +15746,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15753,6 +15914,7 @@
           <t>narrateur|La poule peluche et le doudou. Sami se couche. Le soir, dodo. Maman ferme la porte.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15920,6 +16082,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15938,7 +16101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15983,6 +16146,20 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15997,7 +16174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16184,6 +16361,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
